--- a/00-Administratif/01-ETIQUETTES + NOMBRE  NOTES SEMESTRIELLES/ELMO/ETIQUETTES NUMERIQUES/ELMO_NOTES.xlsx
+++ b/00-Administratif/01-ETIQUETTES + NOMBRE  NOTES SEMESTRIELLES/ELMO/ETIQUETTES NUMERIQUES/ELMO_NOTES.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29212"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\TEXTES\EPSIC\ADMIN\ADMIN_DOMAINE_SANDRO\EXCEL_NOTES_DOMAINE_3\SHARE_POINT_ETIQUETTES_NUMERIQUES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF42CE6A-6098-4416-A272-B7D14EADFA9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{CF42CE6A-6098-4416-A272-B7D14EADFA9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{40D4ADC5-B6B8-4DF8-8848-B80F77E9E519}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{24446EAE-FF7B-4720-8461-B68F93A38A30}"/>
   </bookViews>
@@ -1085,20 +1085,20 @@
     <t>Semestres</t>
   </si>
   <si>
-    <t>EIT.SWISS PQ ELMO</t>
+    <t>Moyenne de «CP» 3 ans</t>
   </si>
   <si>
     <t>Moyenne d'«ECG» 3 ans</t>
   </si>
   <si>
-    <t>Moyenne de «CP» 3 ans</t>
+    <t>EIT.SWISS PQ ELMO</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2114,13 +2114,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8282436-4E2C-455E-A39D-BDA0BF120069}">
   <dimension ref="A1:Z41"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="9" width="8.6640625" customWidth="1"/>
-    <col min="26" max="26" width="11.5546875" style="15"/>
+    <col min="1" max="9" width="8.7109375" customWidth="1"/>
+    <col min="26" max="26" width="11.5703125" style="15"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:26" ht="45" customHeight="1">
       <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
@@ -2136,12 +2136,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:26">
       <c r="Z2" s="15">
         <v>5.5</v>
       </c>
     </row>
-    <row r="3" spans="1:26" s="5" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:26" s="5" customFormat="1" ht="25.15" customHeight="1">
       <c r="A3" s="4" t="s">
         <v>1</v>
       </c>
@@ -2155,12 +2155,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:26">
       <c r="Z4" s="15">
         <v>4.5</v>
       </c>
     </row>
-    <row r="5" spans="1:26" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:26" ht="30" customHeight="1">
       <c r="A5" s="18" t="s">
         <v>2</v>
       </c>
@@ -2176,12 +2176,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:26">
       <c r="Z6" s="15">
         <v>3.5</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:26">
       <c r="A7" s="19" t="s">
         <v>3</v>
       </c>
@@ -2203,12 +2203,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:26">
       <c r="Z8" s="15">
         <v>2.5</v>
       </c>
     </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:26">
       <c r="A9" s="2" t="s">
         <v>6</v>
       </c>
@@ -2226,7 +2226,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:26">
       <c r="A10" s="2" t="s">
         <v>7</v>
       </c>
@@ -2244,9 +2244,13 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A11" s="14"/>
-      <c r="B11" s="14"/>
+    <row r="11" spans="1:26">
+      <c r="A11" s="14">
+        <v>5.5</v>
+      </c>
+      <c r="B11" s="14">
+        <v>5.5</v>
+      </c>
       <c r="C11" s="14"/>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
@@ -2258,10 +2262,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:26" ht="15" thickBot="1">
       <c r="A12" s="14"/>
       <c r="B12" s="14"/>
-      <c r="C12" s="13"/>
+      <c r="C12" s="13">
+        <v>2</v>
+      </c>
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
       <c r="F12" s="14"/>
@@ -2269,13 +2275,13 @@
       <c r="H12" s="14"/>
       <c r="I12" s="3"/>
     </row>
-    <row r="13" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:26" ht="15" thickBot="1">
       <c r="A13" s="13"/>
       <c r="B13" s="13"/>
       <c r="C13" s="13"/>
-      <c r="D13" s="6" t="str">
+      <c r="D13" s="6">
         <f>IF(ISERROR(AVERAGE(BTES1)),"",MROUND(AVERAGE(BTES1),0.5))</f>
-        <v/>
+        <v>4.5</v>
       </c>
       <c r="E13" s="3"/>
       <c r="F13" s="13"/>
@@ -2286,7 +2292,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:26">
       <c r="A14" s="2" t="s">
         <v>8</v>
       </c>
@@ -2301,7 +2307,7 @@
       <c r="H14" s="2"/>
       <c r="I14" s="2"/>
     </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:26">
       <c r="A15" s="2" t="s">
         <v>9</v>
       </c>
@@ -2316,7 +2322,7 @@
       <c r="H15" s="2"/>
       <c r="I15" s="2"/>
     </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:26">
       <c r="A16" s="14"/>
       <c r="B16" s="14"/>
       <c r="C16" s="14"/>
@@ -2327,7 +2333,7 @@
       <c r="H16" s="14"/>
       <c r="I16" s="3"/>
     </row>
-    <row r="17" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:26" ht="15" thickBot="1">
       <c r="A17" s="14"/>
       <c r="B17" s="14"/>
       <c r="C17" s="13"/>
@@ -2338,7 +2344,7 @@
       <c r="H17" s="13"/>
       <c r="I17" s="3"/>
     </row>
-    <row r="18" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:26" ht="15" thickBot="1">
       <c r="A18" s="13"/>
       <c r="B18" s="13"/>
       <c r="C18" s="13"/>
@@ -2355,7 +2361,7 @@
         <v/>
       </c>
     </row>
-    <row r="19" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:26">
       <c r="A19" s="2" t="s">
         <v>10</v>
       </c>
@@ -2370,7 +2376,7 @@
       <c r="H19" s="2"/>
       <c r="I19" s="2"/>
     </row>
-    <row r="20" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:26">
       <c r="A20" s="2" t="s">
         <v>11</v>
       </c>
@@ -2385,7 +2391,7 @@
       <c r="H20" s="2"/>
       <c r="I20" s="2"/>
     </row>
-    <row r="21" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:26">
       <c r="A21" s="14"/>
       <c r="B21" s="14"/>
       <c r="C21" s="14"/>
@@ -2396,7 +2402,7 @@
       <c r="H21" s="14"/>
       <c r="I21" s="3"/>
     </row>
-    <row r="22" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:26" ht="15" thickBot="1">
       <c r="A22" s="13"/>
       <c r="B22" s="13"/>
       <c r="C22" s="13"/>
@@ -2407,7 +2413,7 @@
       <c r="H22" s="13"/>
       <c r="I22" s="3"/>
     </row>
-    <row r="23" spans="1:26" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:26" ht="15" customHeight="1" thickBot="1">
       <c r="A23" s="13"/>
       <c r="B23" s="13"/>
       <c r="C23" s="13"/>
@@ -2425,7 +2431,7 @@
       </c>
       <c r="Z23" s="16"/>
     </row>
-    <row r="24" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:26" ht="15" thickBot="1">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
@@ -2436,15 +2442,15 @@
       <c r="H24" s="2"/>
       <c r="I24" s="2"/>
     </row>
-    <row r="25" spans="1:26" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:26" ht="15.6" thickTop="1" thickBot="1">
       <c r="A25" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
-      <c r="D25" s="7" t="str">
+      <c r="D25" s="7">
         <f>IF(ISERROR(AVERAGE(BTES1MOY,DTES1MOY,TTRS1MOY)),"",MROUND(AVERAGE(BTES1MOY,DTES1MOY,TTRS1MOY),0.5))</f>
-        <v/>
+        <v>4.5</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" s="2" t="s">
@@ -2457,8 +2463,8 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="1:26" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
-    <row r="27" spans="1:26" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:26" ht="15" thickTop="1"/>
+    <row r="27" spans="1:26" s="1" customFormat="1" ht="30" customHeight="1">
       <c r="A27" s="18" t="s">
         <v>13</v>
       </c>
@@ -2472,7 +2478,7 @@
       <c r="I27" s="18"/>
       <c r="Z27" s="15"/>
     </row>
-    <row r="28" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:26">
       <c r="A28" s="2" t="s">
         <v>14</v>
       </c>
@@ -2487,7 +2493,7 @@
       <c r="H28" s="2"/>
       <c r="I28" s="2"/>
     </row>
-    <row r="29" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:26">
       <c r="A29" s="14"/>
       <c r="B29" s="14"/>
       <c r="C29" s="14"/>
@@ -2498,7 +2504,7 @@
       <c r="H29" s="14"/>
       <c r="I29" s="3"/>
     </row>
-    <row r="30" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:26" ht="15" thickBot="1">
       <c r="A30" s="13"/>
       <c r="B30" s="13"/>
       <c r="C30" s="13"/>
@@ -2509,7 +2515,7 @@
       <c r="H30" s="13"/>
       <c r="I30" s="3"/>
     </row>
-    <row r="31" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:26" ht="15" thickBot="1">
       <c r="A31" s="13"/>
       <c r="B31" s="13"/>
       <c r="C31" s="13"/>
@@ -2526,7 +2532,7 @@
         <v/>
       </c>
     </row>
-    <row r="32" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:26">
       <c r="A32" s="2" t="s">
         <v>15</v>
       </c>
@@ -2541,7 +2547,7 @@
       <c r="H32" s="2"/>
       <c r="I32" s="2"/>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:9">
       <c r="A33" s="14"/>
       <c r="B33" s="14"/>
       <c r="C33" s="14"/>
@@ -2552,7 +2558,7 @@
       <c r="H33" s="14"/>
       <c r="I33" s="3"/>
     </row>
-    <row r="34" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:9" ht="15" thickBot="1">
       <c r="A34" s="13"/>
       <c r="B34" s="13"/>
       <c r="C34" s="13"/>
@@ -2563,7 +2569,7 @@
       <c r="H34" s="13"/>
       <c r="I34" s="3"/>
     </row>
-    <row r="35" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:9" ht="15" thickBot="1">
       <c r="A35" s="13"/>
       <c r="B35" s="13"/>
       <c r="C35" s="13"/>
@@ -2580,7 +2586,7 @@
         <v/>
       </c>
     </row>
-    <row r="36" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:9" ht="15" thickBot="1">
       <c r="A36" s="2"/>
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
@@ -2591,7 +2597,7 @@
       <c r="H36" s="2"/>
       <c r="I36" s="2"/>
     </row>
-    <row r="37" spans="1:9" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:9" ht="15.6" thickTop="1" thickBot="1">
       <c r="A37" s="2" t="s">
         <v>16</v>
       </c>
@@ -2612,13 +2618,13 @@
         <v/>
       </c>
     </row>
-    <row r="38" spans="1:9" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:9" ht="15" thickTop="1"/>
+    <row r="40" spans="1:9">
       <c r="A40" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:9">
       <c r="A41" s="2" t="s">
         <v>18</v>
       </c>
@@ -2717,13 +2723,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A755BEC-4892-4CED-8175-6C4B918B2990}">
   <dimension ref="A1:Z41"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="9" width="8.6640625" customWidth="1"/>
-    <col min="26" max="26" width="11.5546875" style="15"/>
+    <col min="1" max="9" width="8.7109375" customWidth="1"/>
+    <col min="26" max="26" width="11.5703125" style="15"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:26" ht="45" customHeight="1">
       <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
@@ -2739,12 +2745,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:26">
       <c r="Z2" s="15">
         <v>5.5</v>
       </c>
     </row>
-    <row r="3" spans="1:26" s="5" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:26" s="5" customFormat="1" ht="25.15" customHeight="1">
       <c r="A3" s="4" t="s">
         <v>1</v>
       </c>
@@ -2758,12 +2764,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:26">
       <c r="Z4" s="15">
         <v>4.5</v>
       </c>
     </row>
-    <row r="5" spans="1:26" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:26" ht="30" customHeight="1">
       <c r="A5" s="18" t="s">
         <v>2</v>
       </c>
@@ -2779,12 +2785,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:26">
       <c r="Z6" s="15">
         <v>3.5</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:26">
       <c r="A7" s="19" t="s">
         <v>19</v>
       </c>
@@ -2806,12 +2812,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:26">
       <c r="Z8" s="15">
         <v>2.5</v>
       </c>
     </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:26">
       <c r="A9" s="2" t="s">
         <v>6</v>
       </c>
@@ -2829,7 +2835,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:26">
       <c r="A10" s="2" t="s">
         <v>7</v>
       </c>
@@ -2847,7 +2853,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:26">
       <c r="A11" s="14"/>
       <c r="B11" s="14"/>
       <c r="C11" s="14"/>
@@ -2861,7 +2867,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:26" ht="15" thickBot="1">
       <c r="A12" s="13"/>
       <c r="B12" s="13"/>
       <c r="C12" s="13"/>
@@ -2872,7 +2878,7 @@
       <c r="H12" s="13"/>
       <c r="I12" s="3"/>
     </row>
-    <row r="13" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:26" ht="15" thickBot="1">
       <c r="A13" s="13"/>
       <c r="B13" s="13"/>
       <c r="C13" s="13"/>
@@ -2889,7 +2895,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:26">
       <c r="A14" s="2" t="s">
         <v>8</v>
       </c>
@@ -2904,7 +2910,7 @@
       <c r="H14" s="2"/>
       <c r="I14" s="2"/>
     </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:26">
       <c r="A15" s="2" t="s">
         <v>9</v>
       </c>
@@ -2919,7 +2925,7 @@
       <c r="H15" s="2"/>
       <c r="I15" s="2"/>
     </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:26">
       <c r="A16" s="14"/>
       <c r="B16" s="14"/>
       <c r="C16" s="13"/>
@@ -2930,7 +2936,7 @@
       <c r="H16" s="13"/>
       <c r="I16" s="3"/>
     </row>
-    <row r="17" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:26" ht="15" thickBot="1">
       <c r="A17" s="14"/>
       <c r="B17" s="14"/>
       <c r="C17" s="13"/>
@@ -2941,7 +2947,7 @@
       <c r="H17" s="13"/>
       <c r="I17" s="3"/>
     </row>
-    <row r="18" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:26" ht="15" thickBot="1">
       <c r="A18" s="13"/>
       <c r="B18" s="13"/>
       <c r="C18" s="13"/>
@@ -2958,7 +2964,7 @@
         <v/>
       </c>
     </row>
-    <row r="19" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:26">
       <c r="A19" s="2" t="s">
         <v>21</v>
       </c>
@@ -2973,7 +2979,7 @@
       <c r="H19" s="2"/>
       <c r="I19" s="2"/>
     </row>
-    <row r="20" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:26">
       <c r="A20" s="2" t="s">
         <v>22</v>
       </c>
@@ -2989,7 +2995,7 @@
       <c r="I20" s="2"/>
       <c r="O20" s="13"/>
     </row>
-    <row r="21" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:26">
       <c r="A21" s="14"/>
       <c r="B21" s="14"/>
       <c r="C21" s="14"/>
@@ -3000,7 +3006,7 @@
       <c r="H21" s="14"/>
       <c r="I21" s="3"/>
     </row>
-    <row r="22" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:26" ht="15" thickBot="1">
       <c r="A22" s="13"/>
       <c r="B22" s="13"/>
       <c r="C22" s="13"/>
@@ -3011,7 +3017,7 @@
       <c r="H22" s="13"/>
       <c r="I22" s="3"/>
     </row>
-    <row r="23" spans="1:26" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:26" ht="15" customHeight="1" thickBot="1">
       <c r="A23" s="13"/>
       <c r="B23" s="13"/>
       <c r="C23" s="13"/>
@@ -3029,7 +3035,7 @@
       </c>
       <c r="Z23" s="16"/>
     </row>
-    <row r="24" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:26" ht="15" thickBot="1">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
@@ -3040,7 +3046,7 @@
       <c r="H24" s="2"/>
       <c r="I24" s="2"/>
     </row>
-    <row r="25" spans="1:26" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:26" ht="15.6" thickTop="1" thickBot="1">
       <c r="A25" s="2" t="s">
         <v>12</v>
       </c>
@@ -3061,8 +3067,8 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="1:26" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
-    <row r="27" spans="1:26" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:26" ht="15" thickTop="1"/>
+    <row r="27" spans="1:26" s="1" customFormat="1" ht="30" customHeight="1">
       <c r="A27" s="18" t="s">
         <v>13</v>
       </c>
@@ -3076,7 +3082,7 @@
       <c r="I27" s="18"/>
       <c r="Z27" s="15"/>
     </row>
-    <row r="28" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:26">
       <c r="A28" s="2" t="s">
         <v>14</v>
       </c>
@@ -3091,7 +3097,7 @@
       <c r="H28" s="2"/>
       <c r="I28" s="2"/>
     </row>
-    <row r="29" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:26">
       <c r="A29" s="14"/>
       <c r="B29" s="14"/>
       <c r="C29" s="14"/>
@@ -3102,7 +3108,7 @@
       <c r="H29" s="14"/>
       <c r="I29" s="3"/>
     </row>
-    <row r="30" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:26" ht="15" thickBot="1">
       <c r="A30" s="13"/>
       <c r="B30" s="13"/>
       <c r="C30" s="13"/>
@@ -3113,7 +3119,7 @@
       <c r="H30" s="13"/>
       <c r="I30" s="3"/>
     </row>
-    <row r="31" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:26" ht="15" thickBot="1">
       <c r="A31" s="13"/>
       <c r="B31" s="13"/>
       <c r="C31" s="13"/>
@@ -3130,7 +3136,7 @@
         <v/>
       </c>
     </row>
-    <row r="32" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:26">
       <c r="A32" s="2"/>
       <c r="B32" s="2"/>
       <c r="C32" s="2"/>
@@ -3143,7 +3149,7 @@
       <c r="H32" s="2"/>
       <c r="I32" s="2"/>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:9">
       <c r="A33" s="14"/>
       <c r="B33" s="14"/>
       <c r="C33" s="14"/>
@@ -3154,7 +3160,7 @@
       <c r="H33" s="14"/>
       <c r="I33" s="3"/>
     </row>
-    <row r="34" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:9" ht="15" thickBot="1">
       <c r="A34" s="13"/>
       <c r="B34" s="13"/>
       <c r="C34" s="13"/>
@@ -3165,7 +3171,7 @@
       <c r="H34" s="13"/>
       <c r="I34" s="3"/>
     </row>
-    <row r="35" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:9" ht="15" thickBot="1">
       <c r="A35" s="13"/>
       <c r="B35" s="13"/>
       <c r="C35" s="13"/>
@@ -3182,7 +3188,7 @@
         <v/>
       </c>
     </row>
-    <row r="36" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:9" ht="15" thickBot="1">
       <c r="A36" s="2"/>
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
@@ -3193,7 +3199,7 @@
       <c r="H36" s="2"/>
       <c r="I36" s="2"/>
     </row>
-    <row r="37" spans="1:9" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:9" ht="15.6" thickTop="1" thickBot="1">
       <c r="A37" s="2" t="s">
         <v>16</v>
       </c>
@@ -3214,13 +3220,13 @@
         <v/>
       </c>
     </row>
-    <row r="38" spans="1:9" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:9" ht="15" thickTop="1"/>
+    <row r="40" spans="1:9">
       <c r="A40" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:9">
       <c r="A41" s="2" t="s">
         <v>18</v>
       </c>
@@ -3345,13 +3351,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF6BE34D-5599-494B-B9C5-C1E68C93A225}">
   <dimension ref="A1:Z41"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="9" width="8.6640625" customWidth="1"/>
-    <col min="26" max="26" width="11.5546875" style="15"/>
+    <col min="1" max="9" width="8.7109375" customWidth="1"/>
+    <col min="26" max="26" width="11.5703125" style="15"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:26" ht="45" customHeight="1">
       <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
@@ -3367,12 +3373,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:26">
       <c r="Z2" s="15">
         <v>5.5</v>
       </c>
     </row>
-    <row r="3" spans="1:26" s="5" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:26" s="5" customFormat="1" ht="25.15" customHeight="1">
       <c r="A3" s="4" t="s">
         <v>1</v>
       </c>
@@ -3386,12 +3392,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:26">
       <c r="Z4" s="15">
         <v>4.5</v>
       </c>
     </row>
-    <row r="5" spans="1:26" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:26" ht="30" customHeight="1">
       <c r="A5" s="18" t="s">
         <v>2</v>
       </c>
@@ -3407,12 +3413,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:26">
       <c r="Z6" s="15">
         <v>3.5</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:26">
       <c r="A7" s="19" t="s">
         <v>23</v>
       </c>
@@ -3434,12 +3440,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:26">
       <c r="Z8" s="15">
         <v>2.5</v>
       </c>
     </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:26">
       <c r="A9" s="2" t="s">
         <v>8</v>
       </c>
@@ -3457,7 +3463,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:26">
       <c r="A10" s="2" t="s">
         <v>9</v>
       </c>
@@ -3475,7 +3481,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:26">
       <c r="A11" s="14"/>
       <c r="B11" s="14"/>
       <c r="C11" s="13"/>
@@ -3489,7 +3495,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:26" ht="15" thickBot="1">
       <c r="A12" s="14"/>
       <c r="B12" s="14"/>
       <c r="C12" s="13"/>
@@ -3500,7 +3506,7 @@
       <c r="H12" s="13"/>
       <c r="I12" s="3"/>
     </row>
-    <row r="13" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:26" ht="15" thickBot="1">
       <c r="A13" s="13"/>
       <c r="B13" s="13"/>
       <c r="C13" s="13"/>
@@ -3517,7 +3523,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:26">
       <c r="A14" s="2" t="s">
         <v>21</v>
       </c>
@@ -3532,7 +3538,7 @@
       <c r="H14" s="2"/>
       <c r="I14" s="2"/>
     </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:26">
       <c r="A15" s="2" t="s">
         <v>22</v>
       </c>
@@ -3547,7 +3553,7 @@
       <c r="H15" s="2"/>
       <c r="I15" s="2"/>
     </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:26">
       <c r="A16" s="14"/>
       <c r="B16" s="14"/>
       <c r="C16" s="14"/>
@@ -3558,7 +3564,7 @@
       <c r="H16" s="14"/>
       <c r="I16" s="3"/>
     </row>
-    <row r="17" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:26" ht="15" thickBot="1">
       <c r="A17" s="14"/>
       <c r="B17" s="14"/>
       <c r="C17" s="13"/>
@@ -3569,7 +3575,7 @@
       <c r="H17" s="13"/>
       <c r="I17" s="3"/>
     </row>
-    <row r="18" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:26" ht="15" thickBot="1">
       <c r="A18" s="13"/>
       <c r="B18" s="13"/>
       <c r="C18" s="13"/>
@@ -3586,7 +3592,7 @@
         <v/>
       </c>
     </row>
-    <row r="19" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:26">
       <c r="A19" s="2"/>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
@@ -3597,7 +3603,7 @@
       <c r="H19" s="2"/>
       <c r="I19" s="2"/>
     </row>
-    <row r="20" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:26">
       <c r="A20" s="2"/>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
@@ -3608,7 +3614,7 @@
       <c r="H20" s="2"/>
       <c r="I20" s="2"/>
     </row>
-    <row r="21" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:26">
       <c r="A21" s="2"/>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
@@ -3619,7 +3625,7 @@
       <c r="H21" s="2"/>
       <c r="I21" s="2"/>
     </row>
-    <row r="22" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:26">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
@@ -3630,7 +3636,7 @@
       <c r="H22" s="2"/>
       <c r="I22" s="2"/>
     </row>
-    <row r="23" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:26" ht="15" customHeight="1">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
@@ -3642,7 +3648,7 @@
       <c r="I23" s="2"/>
       <c r="Z23" s="16"/>
     </row>
-    <row r="24" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:26" ht="15" thickBot="1">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
@@ -3653,7 +3659,7 @@
       <c r="H24" s="2"/>
       <c r="I24" s="2"/>
     </row>
-    <row r="25" spans="1:26" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:26" ht="15.6" thickTop="1" thickBot="1">
       <c r="A25" s="2" t="s">
         <v>12</v>
       </c>
@@ -3674,8 +3680,8 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="1:26" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
-    <row r="27" spans="1:26" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:26" ht="15" thickTop="1"/>
+    <row r="27" spans="1:26" s="1" customFormat="1" ht="30" customHeight="1">
       <c r="A27" s="18" t="s">
         <v>13</v>
       </c>
@@ -3689,7 +3695,7 @@
       <c r="I27" s="18"/>
       <c r="Z27" s="15"/>
     </row>
-    <row r="28" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:26">
       <c r="A28" s="2" t="s">
         <v>14</v>
       </c>
@@ -3704,7 +3710,7 @@
       <c r="H28" s="2"/>
       <c r="I28" s="2"/>
     </row>
-    <row r="29" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:26">
       <c r="A29" s="14"/>
       <c r="B29" s="14"/>
       <c r="C29" s="14"/>
@@ -3715,7 +3721,7 @@
       <c r="H29" s="14"/>
       <c r="I29" s="3"/>
     </row>
-    <row r="30" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:26" ht="15" thickBot="1">
       <c r="A30" s="13"/>
       <c r="B30" s="13"/>
       <c r="C30" s="13"/>
@@ -3726,7 +3732,7 @@
       <c r="H30" s="13"/>
       <c r="I30" s="3"/>
     </row>
-    <row r="31" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:26" ht="15" thickBot="1">
       <c r="A31" s="13"/>
       <c r="B31" s="13"/>
       <c r="C31" s="13"/>
@@ -3743,7 +3749,7 @@
         <v/>
       </c>
     </row>
-    <row r="32" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:26">
       <c r="A32" s="2" t="s">
         <v>15</v>
       </c>
@@ -3758,7 +3764,7 @@
       <c r="H32" s="2"/>
       <c r="I32" s="2"/>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:9">
       <c r="A33" s="14"/>
       <c r="B33" s="14"/>
       <c r="C33" s="14"/>
@@ -3769,7 +3775,7 @@
       <c r="H33" s="14"/>
       <c r="I33" s="3"/>
     </row>
-    <row r="34" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:9" ht="15" thickBot="1">
       <c r="A34" s="13"/>
       <c r="B34" s="13"/>
       <c r="C34" s="13"/>
@@ -3780,7 +3786,7 @@
       <c r="H34" s="13"/>
       <c r="I34" s="3"/>
     </row>
-    <row r="35" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:9" ht="15" thickBot="1">
       <c r="A35" s="13"/>
       <c r="B35" s="13"/>
       <c r="C35" s="13"/>
@@ -3797,7 +3803,7 @@
         <v/>
       </c>
     </row>
-    <row r="36" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:9" ht="15" thickBot="1">
       <c r="A36" s="2"/>
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
@@ -3808,7 +3814,7 @@
       <c r="H36" s="2"/>
       <c r="I36" s="2"/>
     </row>
-    <row r="37" spans="1:9" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:9" ht="15.6" thickTop="1" thickBot="1">
       <c r="A37" s="2" t="s">
         <v>16</v>
       </c>
@@ -3829,13 +3835,13 @@
         <v/>
       </c>
     </row>
-    <row r="38" spans="1:9" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:9" ht="15" thickTop="1"/>
+    <row r="40" spans="1:9">
       <c r="A40" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:9">
       <c r="A41" s="2" t="s">
         <v>18</v>
       </c>
@@ -3902,12 +3908,12 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A799CF54-4FED-421D-9D1B-92D66E0AA9DE}">
   <dimension ref="A1:V30"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="9" width="8.6640625" customWidth="1"/>
+    <col min="1" max="9" width="8.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:22" ht="45" customHeight="1">
       <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
@@ -3920,7 +3926,7 @@
       <c r="H1" s="17"/>
       <c r="I1" s="17"/>
     </row>
-    <row r="3" spans="1:22" s="5" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:22" s="5" customFormat="1" ht="25.15" customHeight="1">
       <c r="A3" s="4" t="s">
         <v>1</v>
       </c>
@@ -3931,7 +3937,7 @@
       <c r="H3" s="10"/>
       <c r="I3" s="10"/>
     </row>
-    <row r="5" spans="1:22" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:22" ht="30" customHeight="1">
       <c r="A5" s="18" t="s">
         <v>2</v>
       </c>
@@ -3944,7 +3950,7 @@
       <c r="H5" s="18"/>
       <c r="I5" s="18"/>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:22">
       <c r="A7" s="19" t="s">
         <v>25</v>
       </c>
@@ -3958,27 +3964,27 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="8" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:22" ht="15" thickBot="1">
       <c r="V8" s="12">
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:22" ht="15" thickBot="1">
       <c r="A9" s="20" t="s">
         <v>3</v>
       </c>
       <c r="B9" s="20"/>
       <c r="C9" s="21"/>
-      <c r="D9" s="6" t="str">
+      <c r="D9" s="6">
         <f>CPS1MOY</f>
-        <v/>
+        <v>4.5</v>
       </c>
       <c r="E9" s="2"/>
       <c r="V9" s="12">
         <v>1.5</v>
       </c>
     </row>
-    <row r="10" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:22" ht="15" thickBot="1">
       <c r="A10" s="20" t="s">
         <v>5</v>
       </c>
@@ -3993,7 +3999,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:22" ht="15" thickBot="1">
       <c r="A11" s="20" t="s">
         <v>19</v>
       </c>
@@ -4005,7 +4011,7 @@
       </c>
       <c r="E11" s="2"/>
     </row>
-    <row r="12" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:22" ht="15" thickBot="1">
       <c r="A12" s="20" t="s">
         <v>20</v>
       </c>
@@ -4017,7 +4023,7 @@
       </c>
       <c r="E12" s="2"/>
     </row>
-    <row r="13" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:22" ht="15" thickBot="1">
       <c r="A13" s="20" t="s">
         <v>23</v>
       </c>
@@ -4029,7 +4035,7 @@
       </c>
       <c r="E13" s="2"/>
     </row>
-    <row r="14" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:22" ht="15" thickBot="1">
       <c r="A14" s="20" t="s">
         <v>24</v>
       </c>
@@ -4041,27 +4047,27 @@
       </c>
       <c r="E14" s="2"/>
     </row>
-    <row r="15" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:22" ht="15" thickBot="1">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
     </row>
-    <row r="16" spans="1:22" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:22" ht="15.6" thickTop="1" thickBot="1">
       <c r="A16" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
-      <c r="D16" s="7" t="str">
+      <c r="D16" s="7">
         <f>IF(ISERROR(AVERAGE(D9:D14)),"",MROUND(AVERAGE(D9:D14),0.5))</f>
-        <v/>
+        <v>4.5</v>
       </c>
       <c r="E16" s="2"/>
     </row>
-    <row r="17" spans="1:9" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
-    <row r="18" spans="1:9" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:9" ht="15" thickTop="1"/>
+    <row r="18" spans="1:9" s="1" customFormat="1" ht="30" customHeight="1">
       <c r="A18" s="18" t="s">
         <v>13</v>
       </c>
@@ -4074,8 +4080,8 @@
       <c r="H18" s="18"/>
       <c r="I18" s="18"/>
     </row>
-    <row r="19" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="20" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:9" ht="15" thickBot="1"/>
+    <row r="20" spans="1:9" ht="15" thickBot="1">
       <c r="A20" s="20" t="s">
         <v>3</v>
       </c>
@@ -4086,7 +4092,7 @@
         <v/>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:9" ht="15" thickBot="1">
       <c r="A21" s="20" t="s">
         <v>5</v>
       </c>
@@ -4097,7 +4103,7 @@
         <v/>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:9" ht="15" thickBot="1">
       <c r="A22" s="20" t="s">
         <v>19</v>
       </c>
@@ -4108,7 +4114,7 @@
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:9" ht="15" thickBot="1">
       <c r="A23" s="20" t="s">
         <v>20</v>
       </c>
@@ -4119,7 +4125,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:9" ht="15" thickBot="1">
       <c r="A24" s="20" t="s">
         <v>23</v>
       </c>
@@ -4130,7 +4136,7 @@
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:9" ht="15" thickBot="1">
       <c r="A25" s="20" t="s">
         <v>24</v>
       </c>
@@ -4141,14 +4147,14 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:9" ht="15" thickBot="1">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
       <c r="D26" s="2"/>
       <c r="E26" s="2"/>
     </row>
-    <row r="27" spans="1:9" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:9" ht="15.6" thickTop="1" thickBot="1">
       <c r="A27" s="2" t="s">
         <v>27</v>
       </c>
@@ -4159,13 +4165,13 @@
         <v/>
       </c>
     </row>
-    <row r="28" spans="1:9" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:9" ht="15" thickTop="1"/>
+    <row r="29" spans="1:9">
       <c r="A29" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:9">
       <c r="A30" s="2" t="s">
         <v>18</v>
       </c>
@@ -4173,6 +4179,12 @@
   </sheetData>
   <sheetProtection sheet="1" selectLockedCells="1"/>
   <mergeCells count="16">
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="A24:C24"/>
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A5:I5"/>
     <mergeCell ref="A7:C7"/>
@@ -4183,12 +4195,6 @@
     <mergeCell ref="A12:C12"/>
     <mergeCell ref="A13:C13"/>
     <mergeCell ref="A14:C14"/>
-    <mergeCell ref="A25:C25"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="A24:C24"/>
   </mergeCells>
   <conditionalFormatting sqref="D9:D14">
     <cfRule type="containsBlanks" dxfId="4" priority="4">
@@ -4231,11 +4237,11 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3874C8AB-05B1-4391-9816-BAA6BC768905}">
   <dimension ref="A1:G1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="14.45"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7">
       <c r="A1" s="22" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B1" s="22"/>
       <c r="C1" s="22"/>
@@ -4259,15 +4265,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100F7262808F74C1A479C3BB44A303B6A0F" ma:contentTypeVersion="16" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="53ca5ba934d9ea82b208c5ebaa87ee73">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="81e70d26-bf48-4cf6-8ac1-a02ba5208bf1" xmlns:ns3="28ecda99-baeb-4159-826c-8d3ebe501c98" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="61005504990099e8d9d64d1794496304" ns2:_="" ns3:_="">
     <xsd:import namespace="81e70d26-bf48-4cf6-8ac1-a02ba5208bf1"/>
@@ -4502,6 +4499,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -4514,24 +4520,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B09B4E12-C5B5-423D-A5B0-596A57297A8E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8AFB0D1E-F2E8-4EDD-8681-BD64330BFF8E}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8AFB0D1E-F2E8-4EDD-8681-BD64330BFF8E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B09B4E12-C5B5-423D-A5B0-596A57297A8E}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A0CD9735-D523-4BAA-9E32-583B1ED165D6}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="81e70d26-bf48-4cf6-8ac1-a02ba5208bf1"/>
-    <ds:schemaRef ds:uri="28ecda99-baeb-4159-826c-8d3ebe501c98"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A0CD9735-D523-4BAA-9E32-583B1ED165D6}"/>
 </file>